--- a/data/trans_orig/P1416-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2007</t>
+          <t>Población con diagnóstico de alergias crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>40715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69732</t>
+          <t>68696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81044</t>
+          <t>81261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118736</t>
+          <t>117720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>130917</t>
+          <t>131059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>178570</t>
+          <t>177151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>961991</t>
+          <t>963027</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>991292</t>
+          <t>991008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1196377</t>
+          <t>1197393</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1234069</t>
+          <t>1233852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2168265</t>
+          <t>2169684</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2215918</t>
+          <t>2215776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96480</t>
+          <t>97937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138820</t>
+          <t>138932</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>147060</t>
+          <t>144512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>194045</t>
+          <t>194758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>254820</t>
+          <t>256397</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>319487</t>
+          <t>318027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1554593</t>
+          <t>1554481</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1596933</t>
+          <t>1595476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1393628</t>
+          <t>1392915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1440613</t>
+          <t>1443161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2961599</t>
+          <t>2963059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3026266</t>
+          <t>3024689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37813</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65673</t>
+          <t>66629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41980</t>
+          <t>42095</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72397</t>
+          <t>72815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85047</t>
+          <t>84409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126087</t>
+          <t>125543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485735</t>
+          <t>484779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>513595</t>
+          <t>514782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>404015</t>
+          <t>403597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>434432</t>
+          <t>434317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>901733</t>
+          <t>902277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>942773</t>
+          <t>943411</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,79%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194709</t>
+          <t>193186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>253999</t>
+          <t>249909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>289998</t>
+          <t>290318</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>360635</t>
+          <t>357888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>498737</t>
+          <t>501629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>587273</t>
+          <t>590728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3022544</t>
+          <t>3026634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3081834</t>
+          <t>3083357</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3018562</t>
+          <t>3021309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3089199</t>
+          <t>3088879</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6068468</t>
+          <t>6065013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6157004</t>
+          <t>6154112</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2012</t>
+          <t>Población con diagnóstico de alergias crónicas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24888</t>
+          <t>25006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49804</t>
+          <t>50194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51175</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84459</t>
+          <t>85619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123665</t>
+          <t>122682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>924839</t>
+          <t>924449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>949755</t>
+          <t>949637</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1253338</t>
+          <t>1252178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1286622</t>
+          <t>1286106</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2188775</t>
+          <t>2189758</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2229212</t>
+          <t>2228896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89981</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131056</t>
+          <t>130302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125692</t>
+          <t>125817</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173174</t>
+          <t>174217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224587</t>
+          <t>224826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>289366</t>
+          <t>287190</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1831879</t>
+          <t>1832633</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1872954</t>
+          <t>1874653</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1583353</t>
+          <t>1582310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1630835</t>
+          <t>1630710</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3430097</t>
+          <t>3432273</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3494876</t>
+          <t>3494637</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21760</t>
+          <t>21722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44579</t>
+          <t>46659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32162</t>
+          <t>32296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59624</t>
+          <t>59912</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>60849</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96722</t>
+          <t>96630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>436602</t>
+          <t>434522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>459421</t>
+          <t>459459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>399007</t>
+          <t>398719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426469</t>
+          <t>426335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>843091</t>
+          <t>843183</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>879480</t>
+          <t>878964</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148786</t>
+          <t>150138</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202337</t>
+          <t>205884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>227866</t>
+          <t>231609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>290978</t>
+          <t>292701</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395684</t>
+          <t>395235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>479192</t>
+          <t>477837</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3216423</t>
+          <t>3212876</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3269974</t>
+          <t>3268622</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3261977</t>
+          <t>3260254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3325089</t>
+          <t>3321346</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6492523</t>
+          <t>6493878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6576031</t>
+          <t>6576480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2016</t>
+          <t>Población con diagnóstico de alergias crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26522</t>
+          <t>28050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65440</t>
+          <t>65864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>52731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85853</t>
+          <t>84270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>727825</t>
+          <t>726297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>744261</t>
+          <t>743739</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>929220</t>
+          <t>928796</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>957811</t>
+          <t>957530</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1663154</t>
+          <t>1664737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1695784</t>
+          <t>1696276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82708</t>
+          <t>85217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123434</t>
+          <t>124326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148393</t>
+          <t>148231</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>198870</t>
+          <t>196015</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>243131</t>
+          <t>244862</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>309429</t>
+          <t>311098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1952951</t>
+          <t>1952059</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1993677</t>
+          <t>1991168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1789430</t>
+          <t>1792285</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1839907</t>
+          <t>1840069</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3755256</t>
+          <t>3753587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3821554</t>
+          <t>3819823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34407</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63070</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44930</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>75546</t>
+          <t>76832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87810</t>
+          <t>87681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129214</t>
+          <t>130193</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>483816</t>
+          <t>485209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512479</t>
+          <t>511449</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>473594</t>
+          <t>472308</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>504210</t>
+          <t>502293</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>966813</t>
+          <t>965834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008217</t>
+          <t>1008346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142837</t>
+          <t>142741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191958</t>
+          <t>194534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>249360</t>
+          <t>248597</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>314564</t>
+          <t>315315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>406528</t>
+          <t>406607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>489708</t>
+          <t>494260</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3185660</t>
+          <t>3183084</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3234781</t>
+          <t>3234877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3217536</t>
+          <t>3216785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3282740</t>
+          <t>3283503</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6420010</t>
+          <t>6415458</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6503190</t>
+          <t>6503111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2023</t>
+          <t>Población con diagnóstico de alergias crónicas en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43528</t>
+          <t>42016</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62192</t>
+          <t>62683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86877</t>
+          <t>86987</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88989</t>
+          <t>89222</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120220</t>
+          <t>121108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>470414</t>
+          <t>471926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>491573</t>
+          <t>492196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665003</t>
+          <t>664893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689688</t>
+          <t>689197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1145602</t>
+          <t>1144714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1176833</t>
+          <t>1176600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>155600</t>
+          <t>170674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>286813</t>
+          <t>291016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163651</t>
+          <t>155873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263947</t>
+          <t>259344</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>375173</t>
+          <t>359656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>530029</t>
+          <t>528130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1998857</t>
+          <t>1994654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2130070</t>
+          <t>2114996</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1960968</t>
+          <t>1965571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2061264</t>
+          <t>2069042</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3980556</t>
+          <t>3982455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4135412</t>
+          <t>4150929</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>38802</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70229</t>
+          <t>68019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76986</t>
+          <t>79333</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109692</t>
+          <t>109866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128037</t>
+          <t>124146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170345</t>
+          <t>168680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>576394</t>
+          <t>578604</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606736</t>
+          <t>607821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549365</t>
+          <t>549191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582071</t>
+          <t>579724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1135335</t>
+          <t>1137000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1177643</t>
+          <t>1181534</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>241543</t>
+          <t>250475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>372994</t>
+          <t>373492</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321213</t>
+          <t>322608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>434153</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>620034</t>
+          <t>614290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>791046</t>
+          <t>791593</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3073242</t>
+          <t>3072744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3204693</t>
+          <t>3195761</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3200907</t>
+          <t>3201699</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3314639</t>
+          <t>3313244</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6291041</t>
+          <t>6290494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6462053</t>
+          <t>6467797</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1416-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40715</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>81185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117720</t>
+          <t>118735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>131059</t>
+          <t>129476</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>177151</t>
+          <t>174203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>963027</t>
+          <t>962969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>991008</t>
+          <t>990743</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1197393</t>
+          <t>1196378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1233852</t>
+          <t>1233928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2169684</t>
+          <t>2172632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2215776</t>
+          <t>2217359</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,48%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97937</t>
+          <t>97869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138932</t>
+          <t>138230</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144512</t>
+          <t>146500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>194758</t>
+          <t>192594</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>256397</t>
+          <t>256662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>318027</t>
+          <t>323710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1554481</t>
+          <t>1555183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1595476</t>
+          <t>1595544</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1392915</t>
+          <t>1395079</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1443161</t>
+          <t>1441173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2963059</t>
+          <t>2957376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3024689</t>
+          <t>3024424</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36626</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66629</t>
+          <t>63752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42095</t>
+          <t>42741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72815</t>
+          <t>73161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84409</t>
+          <t>86118</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125543</t>
+          <t>125248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>484779</t>
+          <t>487656</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514782</t>
+          <t>514400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>403597</t>
+          <t>403251</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>434317</t>
+          <t>433671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>902277</t>
+          <t>902572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>943411</t>
+          <t>941702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193186</t>
+          <t>188622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>249909</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>290318</t>
+          <t>291854</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>357888</t>
+          <t>358099</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>499853</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>590728</t>
+          <t>593898</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3026634</t>
+          <t>3025900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3083357</t>
+          <t>3087921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3021309</t>
+          <t>3021098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3088879</t>
+          <t>3087343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6065013</t>
+          <t>6061843</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6154112</t>
+          <t>6155888</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25006</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50194</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>52743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85619</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>83544</t>
+          <t>83293</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122682</t>
+          <t>123996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>924449</t>
+          <t>923269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>949637</t>
+          <t>950147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1252178</t>
+          <t>1253533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1286106</t>
+          <t>1285054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2189758</t>
+          <t>2188444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2228896</t>
+          <t>2229147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88282</t>
+          <t>87516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130302</t>
+          <t>130038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125817</t>
+          <t>126172</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>174217</t>
+          <t>173028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224826</t>
+          <t>227220</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287190</t>
+          <t>289352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1832633</t>
+          <t>1832897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1874653</t>
+          <t>1875419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1582310</t>
+          <t>1583499</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1630710</t>
+          <t>1630355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3432273</t>
+          <t>3430111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3494637</t>
+          <t>3492243</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21722</t>
+          <t>22111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46659</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59912</t>
+          <t>60839</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60849</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96630</t>
+          <t>96049</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434522</t>
+          <t>435888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>459459</t>
+          <t>459070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>398719</t>
+          <t>397792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426335</t>
+          <t>424816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>843183</t>
+          <t>843764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>878964</t>
+          <t>879434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,58%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>150138</t>
+          <t>150797</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205884</t>
+          <t>204577</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>231609</t>
+          <t>234372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>292701</t>
+          <t>295728</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395235</t>
+          <t>400343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>477837</t>
+          <t>480357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3212876</t>
+          <t>3214183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3268622</t>
+          <t>3267963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3260254</t>
+          <t>3257227</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3321346</t>
+          <t>3318583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6493878</t>
+          <t>6491358</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6576480</t>
+          <t>6571372</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28050</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37130</t>
+          <t>36100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65864</t>
+          <t>65455</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52731</t>
+          <t>51587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84270</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726297</t>
+          <t>727965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>743739</t>
+          <t>744170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>928796</t>
+          <t>929205</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>957530</t>
+          <t>958560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1664737</t>
+          <t>1663921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1696276</t>
+          <t>1697420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85217</t>
+          <t>82366</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124326</t>
+          <t>124873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,82 +4297,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>6,01%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>172042</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>147038</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>197464</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>7,4%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,93%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>275199</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>243429</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>306120</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>5,99%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>172042</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>148231</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>196015</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>275199</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>244862</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>311098</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1952059</t>
+          <t>1951512</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1991168</t>
+          <t>1994019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,82 +4410,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>93,99%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1742</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1816258</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1790836</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1841262</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,07%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3595</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>3789486</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>3758565</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3821256</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>92,47%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>94,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1742</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1816258</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1792285</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1840069</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,14%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,54%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3595</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>3789486</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>3753587</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3819823</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>92,35%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35437</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61677</t>
+          <t>61615</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>45819</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76832</t>
+          <t>76435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87681</t>
+          <t>86456</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130193</t>
+          <t>130273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485209</t>
+          <t>485271</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>511449</t>
+          <t>513014</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>472308</t>
+          <t>472705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>502293</t>
+          <t>503321</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>965834</t>
+          <t>965754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1008346</t>
+          <t>1009571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>142741</t>
+          <t>143602</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194534</t>
+          <t>194722</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248597</t>
+          <t>252284</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>315315</t>
+          <t>316472</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>406607</t>
+          <t>413280</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494260</t>
+          <t>493470</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3183084</t>
+          <t>3182896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3234877</t>
+          <t>3234016</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3216785</t>
+          <t>3215628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3283503</t>
+          <t>3279816</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6415458</t>
+          <t>6416248</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6503111</t>
+          <t>6496438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>30415</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>73970</t>
+          <t>84453</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>62683</t>
+          <t>72184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86987</t>
+          <t>98126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>104385</t>
+          <t>116702</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89222</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121108</t>
+          <t>135467</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>483527</t>
+          <t>545292</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>471926</t>
+          <t>533459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492196</t>
+          <t>554768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>677910</t>
+          <t>735496</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664893</t>
+          <t>721823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>689197</t>
+          <t>747765</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1161437</t>
+          <t>1280789</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1144714</t>
+          <t>1262024</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1176600</t>
+          <t>1296008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751880</t>
+          <t>819949</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751880</t>
+          <t>819949</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751880</t>
+          <t>819949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265822</t>
+          <t>1397491</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265822</t>
+          <t>1397491</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265822</t>
+          <t>1397491</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>239427</t>
+          <t>247972</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>170674</t>
+          <t>212428</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>291016</t>
+          <t>285460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>224443</t>
+          <t>252686</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>155873</t>
+          <t>229421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>259344</t>
+          <t>281607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>463871</t>
+          <t>500658</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359656</t>
+          <t>456990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>528130</t>
+          <t>549273</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,53%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2046243</t>
+          <t>1977753</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1994654</t>
+          <t>1940265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2114996</t>
+          <t>2013297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2000472</t>
+          <t>1904949</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1965571</t>
+          <t>1876028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2069042</t>
+          <t>1928214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4046714</t>
+          <t>3882702</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3982455</t>
+          <t>3834087</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4150929</t>
+          <t>3926370</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>89,57%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2285670</t>
+          <t>2225725</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2285670</t>
+          <t>2225725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2285670</t>
+          <t>2225725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2224915</t>
+          <t>2157635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2224915</t>
+          <t>2157635</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2224915</t>
+          <t>2157635</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4510585</t>
+          <t>4383360</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4510585</t>
+          <t>4383360</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4510585</t>
+          <t>4383360</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>59711</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38802</t>
+          <t>45197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68019</t>
+          <t>77699</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>93943</t>
+          <t>107320</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79333</t>
+          <t>91291</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109866</t>
+          <t>127452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146364</t>
+          <t>167031</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124146</t>
+          <t>145289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168680</t>
+          <t>190881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>594202</t>
+          <t>651876</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>578604</t>
+          <t>633888</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>607821</t>
+          <t>666390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>565114</t>
+          <t>626068</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549191</t>
+          <t>605936</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579724</t>
+          <t>642097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1159316</t>
+          <t>1277944</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1137000</t>
+          <t>1254094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1181534</t>
+          <t>1299686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659057</t>
+          <t>733388</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659057</t>
+          <t>733388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659057</t>
+          <t>733388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305680</t>
+          <t>1444975</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305680</t>
+          <t>1444975</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305680</t>
+          <t>1444975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>322264</t>
+          <t>339933</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>250475</t>
+          <t>301150</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373492</t>
+          <t>380633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>392357</t>
+          <t>444458</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>322608</t>
+          <t>410013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>434153</t>
+          <t>479530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>714620</t>
+          <t>784392</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614290</t>
+          <t>736034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>791593</t>
+          <t>846863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3123972</t>
+          <t>3174921</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3072744</t>
+          <t>3134221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3195761</t>
+          <t>3213704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3243495</t>
+          <t>3266514</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3201699</t>
+          <t>3231442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3313244</t>
+          <t>3300959</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6367467</t>
+          <t>6441434</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6290494</t>
+          <t>6378963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6467797</t>
+          <t>6489792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3446236</t>
+          <t>3514854</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3446236</t>
+          <t>3514854</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3446236</t>
+          <t>3514854</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3635852</t>
+          <t>3710972</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3635852</t>
+          <t>3710972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3635852</t>
+          <t>3710972</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7082087</t>
+          <t>7225826</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7082087</t>
+          <t>7225826</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7082087</t>
+          <t>7225826</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
